--- a/r5-aist-trustworthyai-main/StructureDefinition-trust-ai-device.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-trust-ai-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:13:25+00:00</t>
+    <t>2026-10-02T06:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -572,10 +572,10 @@
     <t>euDatabaseId</t>
   </si>
   <si>
-    <t>Trust AI database registration number</t>
-  </si>
-  <si>
-    <t>The unique registration number assigned to the high-risk AI system in the official Trust AI database.</t>
+    <t>EU database registration number</t>
+  </si>
+  <si>
+    <t>The unique registration number assigned to the high-risk AI system in the official EU database (AI Act Art. 49).</t>
   </si>
   <si>
     <t>AI Act Art. 49 | EU Database Registration</t>
